--- a/AAII_Financials/Yearly/SNAP_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/SNAP_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="92">
   <si>
     <t>SNAP</t>
   </si>
@@ -656,59 +656,59 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="15" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44561</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44196</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43830</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43465</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43100</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42735</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42369</v>
       </c>
-      <c r="L7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M7" s="2" t="s">
         <v>3</v>
       </c>
@@ -718,39 +718,42 @@
       <c r="O7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>4606100</v>
+      </c>
+      <c r="E8" s="3">
         <v>4601800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>4117000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2506600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1715500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1180400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>824900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>404500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>58700</v>
       </c>
-      <c r="L8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M8" s="3" t="s">
         <v>3</v>
       </c>
@@ -760,39 +763,42 @@
       <c r="O8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>2114100</v>
+      </c>
+      <c r="E9" s="3">
         <v>1794800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1750200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1182500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>895800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>798900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>717500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>451700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>182300</v>
       </c>
-      <c r="L9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M9" s="3" t="s">
         <v>3</v>
       </c>
@@ -802,39 +808,42 @@
       <c r="O9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>2492000</v>
+      </c>
+      <c r="E10" s="3">
         <v>2807100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2366800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1324100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>819700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>381600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>107500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>-47200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>-123700</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M10" s="3" t="s">
         <v>3</v>
       </c>
@@ -844,9 +853,12 @@
       <c r="O10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -863,38 +875,39 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>1804600</v>
+      </c>
+      <c r="E12" s="3">
         <v>1932800</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>1503300</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>1063900</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>850300</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>739200</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>1509800</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>183700</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>82200</v>
       </c>
-      <c r="L12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M12" s="3" t="s">
         <v>3</v>
       </c>
@@ -904,9 +917,12 @@
       <c r="O12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -946,27 +962,30 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-      <c r="P13" s="3"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3">
         <v>188900</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G14" s="3">
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3">
         <v>-39900</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I14" s="3" t="s">
         <v>3</v>
       </c>
@@ -982,39 +1001,42 @@
       <c r="M14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
+      <c r="N14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O14" s="3">
         <v>0</v>
       </c>
-      <c r="P14" s="3"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>155700</v>
+      </c>
+      <c r="E15" s="3">
         <v>177900</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>99400</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>64500</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>66000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>65400</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>46100</v>
       </c>
-      <c r="J15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1024,15 +1046,18 @@
       <c r="M15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N15" s="3">
-        <v>0</v>
+      <c r="N15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O15" s="3">
         <v>0</v>
       </c>
-      <c r="P15" s="3"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="3"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1046,38 +1071,39 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>6004500</v>
+      </c>
+      <c r="E17" s="3">
         <v>5997200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>4819100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>3368700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>2779000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2448900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>4310500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>924900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>440400</v>
       </c>
-      <c r="L17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1087,39 +1113,42 @@
       <c r="O17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P17" s="3"/>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q17" s="3"/>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-1398400</v>
+      </c>
+      <c r="E18" s="3">
         <v>-1395300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-702100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-862100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-1063400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-1268500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-3485600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-520400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-381700</v>
       </c>
-      <c r="L18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1129,9 +1158,12 @@
       <c r="O18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P18" s="3"/>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q18" s="3"/>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1148,38 +1180,39 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>126000</v>
+      </c>
+      <c r="E20" s="3">
         <v>16100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>245400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>33100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>55200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>19000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>25600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>1200</v>
       </c>
-      <c r="L20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1189,39 +1222,42 @@
       <c r="O20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P20" s="3"/>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q20" s="3"/>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-1104000</v>
+      </c>
+      <c r="E21" s="3">
         <v>-1177100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-337600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-742200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-921000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-1157800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-3398700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-491200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-365200</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1231,38 +1267,41 @@
       <c r="O21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P21" s="3"/>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q21" s="3"/>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>22000</v>
+      </c>
+      <c r="E22" s="3">
         <v>21500</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>17700</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>97200</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>25000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>3900</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>3500</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>1400</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
-      </c>
-      <c r="L22" s="3" t="s">
-        <v>3</v>
+      <c r="L22" s="3">
+        <v>0</v>
       </c>
       <c r="M22" s="3" t="s">
         <v>3</v>
@@ -1273,39 +1312,42 @@
       <c r="O22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P22" s="3"/>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q22" s="3"/>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-1294400</v>
+      </c>
+      <c r="E23" s="3">
         <v>-1400700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-474400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-926200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-1033300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-1253400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-3463400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-521700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-380500</v>
       </c>
-      <c r="L23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1315,39 +1357,42 @@
       <c r="O23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P23" s="3"/>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q23" s="3"/>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>28100</v>
+      </c>
+      <c r="E24" s="3">
         <v>29000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>13600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>18700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>2500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-18300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-7100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-7600</v>
       </c>
-      <c r="L24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1357,9 +1402,12 @@
       <c r="O24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P24" s="3"/>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q24" s="3"/>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1399,39 +1447,42 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-      <c r="P25" s="3"/>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3"/>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-1322500</v>
+      </c>
+      <c r="E26" s="3">
         <v>-1429700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-488000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-944800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-1033700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-1255900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-3445100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-514600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-372900</v>
       </c>
-      <c r="L26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1441,39 +1492,42 @@
       <c r="O26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P26" s="3"/>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q26" s="3"/>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-1322500</v>
+      </c>
+      <c r="E27" s="3">
         <v>-1429700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-488000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-944800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-1033700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-1255900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-3445100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-514600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-372900</v>
       </c>
-      <c r="L27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1483,9 +1537,12 @@
       <c r="O27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P27" s="3"/>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q27" s="3"/>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1525,9 +1582,12 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-      <c r="P28" s="3"/>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3"/>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1564,12 +1624,15 @@
       <c r="N29" s="3">
         <v>0</v>
       </c>
-      <c r="O29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P29" s="3"/>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="O29" s="3">
+        <v>0</v>
+      </c>
+      <c r="P29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q29" s="3"/>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1609,9 +1672,12 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-      <c r="P30" s="3"/>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3"/>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1651,39 +1717,42 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-      <c r="P31" s="3"/>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3"/>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-126000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-16100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-245400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-33100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-55200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-19000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-25600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-1200</v>
       </c>
-      <c r="L32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M32" s="3" t="s">
         <v>3</v>
       </c>
@@ -1693,39 +1762,42 @@
       <c r="O32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P32" s="3"/>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q32" s="3"/>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-1322500</v>
+      </c>
+      <c r="E33" s="3">
         <v>-1429700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-488000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-944800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-1033700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-1255900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-3445100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-514600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-372900</v>
       </c>
-      <c r="L33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1735,9 +1807,12 @@
       <c r="O33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P33" s="3"/>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q33" s="3"/>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1777,39 +1852,42 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-      <c r="P34" s="3"/>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3"/>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-1322500</v>
+      </c>
+      <c r="E35" s="3">
         <v>-1429700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-488000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-944800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-1033700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-1255900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-3445100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-514600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-372900</v>
       </c>
-      <c r="L35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M35" s="3" t="s">
         <v>3</v>
       </c>
@@ -1819,44 +1897,47 @@
       <c r="O35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P35" s="3"/>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q35" s="3"/>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44561</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44196</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43830</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43465</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43100</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42735</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42369</v>
       </c>
-      <c r="L38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M38" s="2" t="s">
         <v>3</v>
       </c>
@@ -1866,9 +1947,12 @@
       <c r="O38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="P38" s="2"/>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q38" s="2"/>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1885,8 +1969,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1903,38 +1988,39 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1780400</v>
+      </c>
+      <c r="E41" s="3">
         <v>1423100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1993800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>545600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>520300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>387100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>334100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>150100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>640800</v>
       </c>
-      <c r="L41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M41" s="3" t="s">
         <v>3</v>
       </c>
@@ -1944,38 +2030,41 @@
       <c r="O41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P41" s="3"/>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q41" s="3"/>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>1763700</v>
+      </c>
+      <c r="E42" s="3">
         <v>2516000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>1699100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>1991900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>1592500</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>891900</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>1709000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>837200</v>
       </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
-      <c r="L42" s="3" t="s">
-        <v>3</v>
+      <c r="L42" s="3">
+        <v>0</v>
       </c>
       <c r="M42" s="3" t="s">
         <v>3</v>
@@ -1986,39 +2075,42 @@
       <c r="O42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P42" s="3"/>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q42" s="3"/>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1278200</v>
+      </c>
+      <c r="E43" s="3">
         <v>1183100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1068900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>744300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>492200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>355000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>279500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>162700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>44300</v>
       </c>
-      <c r="L43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2028,9 +2120,12 @@
       <c r="O43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P43" s="3"/>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q43" s="3"/>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2070,39 +2165,42 @@
       <c r="O44" s="3">
         <v>0</v>
       </c>
-      <c r="P44" s="3"/>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P44" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="3"/>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>153600</v>
+      </c>
+      <c r="E45" s="3">
         <v>134400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>92200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>56100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>39000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>41900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>44300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>30000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>7400</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2112,39 +2210,42 @@
       <c r="O45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P45" s="3"/>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q45" s="3"/>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>4975800</v>
+      </c>
+      <c r="E46" s="3">
         <v>5256600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>4854000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>3338000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2644000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1675900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2366800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1180000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>692600</v>
       </c>
-      <c r="L46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2154,39 +2255,42 @@
       <c r="O46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P46" s="3"/>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q46" s="3"/>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
+      <c r="D47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E47" s="3">
         <v>252300</v>
       </c>
-      <c r="E47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G47" s="3">
+      <c r="G47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H47" s="3">
         <v>55000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>43600</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>22700</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>11800</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>9100</v>
       </c>
-      <c r="L47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2196,39 +2300,42 @@
       <c r="O47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P47" s="3"/>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q47" s="3"/>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>927200</v>
+      </c>
+      <c r="E48" s="3">
         <v>642700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>524900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>448400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>449100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>212600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>166800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>100600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>44100</v>
       </c>
-      <c r="L48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2238,39 +2345,42 @@
       <c r="O48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P48" s="3"/>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q48" s="3"/>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1838100</v>
+      </c>
+      <c r="E49" s="3">
         <v>1850600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1866100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1045200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>853300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>758400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>806400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>395100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>177200</v>
       </c>
-      <c r="L49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2280,9 +2390,12 @@
       <c r="O49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P49" s="3"/>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q49" s="3"/>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2322,9 +2435,12 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-      <c r="P50" s="3"/>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3"/>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2364,39 +2480,42 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-      <c r="P51" s="3"/>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3"/>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>226600</v>
+      </c>
+      <c r="E52" s="3">
         <v>27300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>291300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>192600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>10600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>23600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>59000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>35300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>16000</v>
       </c>
-      <c r="L52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2406,9 +2525,12 @@
       <c r="O52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P52" s="3"/>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q52" s="3"/>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2448,39 +2570,42 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-      <c r="P53" s="3"/>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3"/>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>7967800</v>
+      </c>
+      <c r="E54" s="3">
         <v>8029500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>7536300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>5024200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>4011900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2714100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>3421600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1722800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>938900</v>
       </c>
-      <c r="L54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2490,9 +2615,12 @@
       <c r="O54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P54" s="3"/>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q54" s="3"/>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2509,8 +2637,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2527,38 +2656,39 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>279000</v>
+      </c>
+      <c r="E57" s="3">
         <v>181800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>125300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>71900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>46900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>30900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>71200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>8400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>700</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2568,9 +2698,12 @@
       <c r="O57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P57" s="3"/>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q57" s="3"/>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2610,39 +2743,42 @@
       <c r="O58" s="3">
         <v>0</v>
       </c>
-      <c r="P58" s="3"/>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="3"/>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>855200</v>
+      </c>
+      <c r="E59" s="3">
         <v>1033800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>726500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>595400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>452800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>261800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>275100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>148300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>155600</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2652,39 +2788,42 @@
       <c r="O59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P59" s="3"/>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q59" s="3"/>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1134100</v>
+      </c>
+      <c r="E60" s="3">
         <v>1215600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>851800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>667300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>499700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>292700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>346300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>156700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>156300</v>
       </c>
-      <c r="L60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2694,39 +2833,42 @@
       <c r="O60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P60" s="3"/>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q60" s="3"/>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>3749400</v>
+      </c>
+      <c r="E61" s="3">
         <v>3742500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2253100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1675200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>891800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>16800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>16000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>15100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>13500</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
@@ -2736,39 +2878,42 @@
       <c r="O61" s="3">
         <v>0</v>
       </c>
-      <c r="P61" s="3"/>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="3"/>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>670100</v>
+      </c>
+      <c r="E62" s="3">
         <v>490700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>641300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>351800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>360600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>93600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>67000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>32000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>5000</v>
       </c>
-      <c r="L62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2778,9 +2923,12 @@
       <c r="O62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P62" s="3"/>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q62" s="3"/>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2820,9 +2968,12 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-      <c r="P63" s="3"/>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3"/>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2862,9 +3013,12 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-      <c r="P64" s="3"/>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3"/>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2904,39 +3058,42 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-      <c r="P65" s="3"/>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3"/>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>5553600</v>
+      </c>
+      <c r="E66" s="3">
         <v>5448800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>3746100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2694300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1752000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>403100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>429200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>203900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>174800</v>
       </c>
-      <c r="L66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M66" s="3" t="s">
         <v>3</v>
       </c>
@@ -2946,9 +3103,12 @@
       <c r="O66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P66" s="3"/>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q66" s="3"/>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2965,8 +3125,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3006,9 +3167,12 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-      <c r="P68" s="3"/>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3"/>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3048,9 +3212,12 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-      <c r="P69" s="3"/>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3"/>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3090,9 +3257,12 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-      <c r="P70" s="3"/>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3"/>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3132,39 +3302,42 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-      <c r="P71" s="3"/>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3"/>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-11726500</v>
+      </c>
+      <c r="E72" s="3">
         <v>-10214700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-8284500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-7891500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-6945900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-5912600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-4656700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-1207900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-693200</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3174,9 +3347,12 @@
       <c r="O72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P72" s="3"/>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q72" s="3"/>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3216,9 +3392,12 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-      <c r="P73" s="3"/>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3"/>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3258,9 +3437,12 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-      <c r="P74" s="3"/>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3"/>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3300,39 +3482,42 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-      <c r="P75" s="3"/>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3"/>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2414100</v>
+      </c>
+      <c r="E76" s="3">
         <v>2580700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>3790200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2330000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2259900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2311000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2992300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1518900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>764100</v>
       </c>
-      <c r="L76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3342,9 +3527,12 @@
       <c r="O76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P76" s="3"/>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q76" s="3"/>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3384,44 +3572,47 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-      <c r="P77" s="3"/>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3"/>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44561</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44196</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43830</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43465</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43100</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42735</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42369</v>
       </c>
-      <c r="L80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M80" s="2" t="s">
         <v>3</v>
       </c>
@@ -3431,39 +3622,42 @@
       <c r="O80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="P80" s="2"/>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q80" s="2"/>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-1322500</v>
+      </c>
+      <c r="E81" s="3">
         <v>-1429700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-488000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-944800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-1033700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-1255900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-3445100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-514600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-372900</v>
       </c>
-      <c r="L81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M81" s="3" t="s">
         <v>3</v>
       </c>
@@ -3473,9 +3667,12 @@
       <c r="O81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P81" s="3"/>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q81" s="3"/>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3492,38 +3689,39 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>168400</v>
+      </c>
+      <c r="E83" s="3">
         <v>202200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>119100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>86700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>87200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>91600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>61300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>29100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>15300</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M83" s="3" t="s">
         <v>3</v>
       </c>
@@ -3533,9 +3731,12 @@
       <c r="O83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P83" s="3"/>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q83" s="3"/>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3575,9 +3776,12 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-      <c r="P84" s="3"/>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3"/>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3617,9 +3821,12 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-      <c r="P85" s="3"/>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3"/>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3659,9 +3866,12 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-      <c r="P86" s="3"/>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3"/>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3701,9 +3911,12 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-      <c r="P87" s="3"/>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3"/>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3743,39 +3956,42 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-      <c r="P88" s="3"/>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3"/>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>246500</v>
+      </c>
+      <c r="E89" s="3">
         <v>184600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>292900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-167600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-305000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-689900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-734700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-611200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-306600</v>
       </c>
-      <c r="L89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M89" s="3" t="s">
         <v>3</v>
       </c>
@@ -3785,9 +4001,12 @@
       <c r="O89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P89" s="3"/>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q89" s="3"/>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3804,38 +4023,39 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-211700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-129300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-69900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-57800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-36500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-120200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-84500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-66400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-19200</v>
       </c>
-      <c r="L91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M91" s="3" t="s">
         <v>3</v>
       </c>
@@ -3845,9 +4065,12 @@
       <c r="O91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P91" s="3"/>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q91" s="3"/>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3887,9 +4110,12 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-      <c r="P92" s="3"/>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3"/>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3929,39 +4155,42 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-      <c r="P93" s="3"/>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3"/>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>571000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1062300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>90200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-729900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-728600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>694500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1357000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1014300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-100900</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M94" s="3" t="s">
         <v>3</v>
       </c>
@@ -3971,9 +4200,12 @@
       <c r="O94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P94" s="3"/>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q94" s="3"/>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3990,8 +4222,9 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4031,9 +4264,12 @@
       <c r="O96" s="3">
         <v>0</v>
       </c>
-      <c r="P96" s="3"/>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3"/>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4073,9 +4309,12 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-      <c r="P97" s="3"/>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3"/>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4115,9 +4354,12 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-      <c r="P98" s="3"/>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3"/>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4157,39 +4399,42 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-      <c r="P99" s="3"/>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3"/>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-458800</v>
+      </c>
+      <c r="E100" s="3">
         <v>306700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>1065100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>922800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>1165900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>47400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>2265300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>1141900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>650400</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M100" s="3" t="s">
         <v>3</v>
       </c>
@@ -4199,9 +4444,12 @@
       <c r="O100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P100" s="3"/>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q100" s="3"/>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4241,39 +4489,42 @@
       <c r="O101" s="3">
         <v>0</v>
       </c>
-      <c r="P101" s="3"/>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="3"/>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>358700</v>
+      </c>
+      <c r="E102" s="3">
         <v>-570900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>1448200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>25300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>132300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>52000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>173700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-483600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>242800</v>
       </c>
-      <c r="L102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M102" s="3" t="s">
         <v>3</v>
       </c>
@@ -4283,7 +4534,10 @@
       <c r="O102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P102" s="3"/>
+      <c r="P102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/SNAP_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/SNAP_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="92">
   <si>
     <t>SNAP</t>
   </si>
@@ -791,7 +791,7 @@
         <v>798900</v>
       </c>
       <c r="J9" s="3">
-        <v>717500</v>
+        <v>677600</v>
       </c>
       <c r="K9" s="3">
         <v>451700</v>
@@ -836,7 +836,7 @@
         <v>381600</v>
       </c>
       <c r="J10" s="3">
-        <v>107500</v>
+        <v>147400</v>
       </c>
       <c r="K10" s="3">
         <v>-47200</v>
@@ -882,25 +882,25 @@
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>1804600</v>
+        <v>1910900</v>
       </c>
       <c r="E12" s="3">
-        <v>1932800</v>
+        <v>2030900</v>
       </c>
       <c r="F12" s="3">
-        <v>1503300</v>
+        <v>1565500</v>
       </c>
       <c r="G12" s="3">
-        <v>1063900</v>
+        <v>1101600</v>
       </c>
       <c r="H12" s="3">
-        <v>850300</v>
+        <v>883500</v>
       </c>
       <c r="I12" s="3">
-        <v>739200</v>
+        <v>772200</v>
       </c>
       <c r="J12" s="3">
-        <v>1509800</v>
+        <v>1534900</v>
       </c>
       <c r="K12" s="3">
         <v>183700</v>
@@ -971,26 +971,26 @@
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>3</v>
+      <c r="D14" s="3">
+        <v>33700</v>
       </c>
       <c r="E14" s="3">
-        <v>188900</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>3</v>
+        <v>225800</v>
+      </c>
+      <c r="F14" s="3">
+        <v>-292000</v>
+      </c>
+      <c r="G14" s="3">
+        <v>-12900</v>
       </c>
       <c r="H14" s="3">
         <v>-39900</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
+      <c r="I14" s="3">
+        <v>38300</v>
+      </c>
+      <c r="J14" s="3">
+        <v>39900</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>3</v>
@@ -1017,25 +1017,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>155700</v>
+        <v>168400</v>
       </c>
       <c r="E15" s="3">
-        <v>177900</v>
+        <v>152900</v>
       </c>
       <c r="F15" s="3">
-        <v>99400</v>
+        <v>119100</v>
       </c>
       <c r="G15" s="3">
-        <v>64500</v>
+        <v>86700</v>
       </c>
       <c r="H15" s="3">
-        <v>66000</v>
+        <v>87200</v>
       </c>
       <c r="I15" s="3">
-        <v>65400</v>
+        <v>91600</v>
       </c>
       <c r="J15" s="3">
-        <v>46100</v>
+        <v>61300</v>
       </c>
       <c r="K15" s="3" t="s">
         <v>3</v>
@@ -1081,7 +1081,7 @@
         <v>6004500</v>
       </c>
       <c r="E17" s="3">
-        <v>5997200</v>
+        <v>5808200</v>
       </c>
       <c r="F17" s="3">
         <v>4819100</v>
@@ -1090,13 +1090,13 @@
         <v>3368700</v>
       </c>
       <c r="H17" s="3">
-        <v>2779000</v>
+        <v>2818900</v>
       </c>
       <c r="I17" s="3">
-        <v>2448900</v>
+        <v>2417800</v>
       </c>
       <c r="J17" s="3">
-        <v>4310500</v>
+        <v>4270700</v>
       </c>
       <c r="K17" s="3">
         <v>924900</v>
@@ -1126,7 +1126,7 @@
         <v>-1398400</v>
       </c>
       <c r="E18" s="3">
-        <v>-1395300</v>
+        <v>-1206400</v>
       </c>
       <c r="F18" s="3">
         <v>-702100</v>
@@ -1135,13 +1135,13 @@
         <v>-862100</v>
       </c>
       <c r="H18" s="3">
-        <v>-1063400</v>
+        <v>-1103300</v>
       </c>
       <c r="I18" s="3">
-        <v>-1268500</v>
+        <v>-1237300</v>
       </c>
       <c r="J18" s="3">
-        <v>-3485600</v>
+        <v>-3445700</v>
       </c>
       <c r="K18" s="3">
         <v>-520400</v>
@@ -1187,25 +1187,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>126000</v>
+        <v>8700</v>
       </c>
       <c r="E20" s="3">
-        <v>16100</v>
+        <v>5700</v>
       </c>
       <c r="F20" s="3">
-        <v>245400</v>
+        <v>51900</v>
       </c>
       <c r="G20" s="3">
-        <v>33100</v>
+        <v>-2100</v>
       </c>
       <c r="H20" s="3">
-        <v>55200</v>
+        <v>-19100</v>
       </c>
       <c r="I20" s="3">
-        <v>19000</v>
+        <v>1000</v>
       </c>
       <c r="J20" s="3">
-        <v>25600</v>
+        <v>-4500</v>
       </c>
       <c r="K20" s="3">
         <v>100</v>
@@ -1232,25 +1232,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-1104000</v>
+        <v>-1238600</v>
       </c>
       <c r="E21" s="3">
-        <v>-1177100</v>
+        <v>-1059200</v>
       </c>
       <c r="F21" s="3">
-        <v>-337600</v>
+        <v>-634800</v>
       </c>
       <c r="G21" s="3">
-        <v>-742200</v>
+        <v>-773200</v>
       </c>
       <c r="H21" s="3">
-        <v>-921000</v>
+        <v>-997000</v>
       </c>
       <c r="I21" s="3">
-        <v>-1157800</v>
+        <v>-1146700</v>
       </c>
       <c r="J21" s="3">
-        <v>-3398700</v>
+        <v>-3379900</v>
       </c>
       <c r="K21" s="3">
         <v>-491200</v>
@@ -1727,25 +1727,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-126000</v>
+        <v>-8700</v>
       </c>
       <c r="E32" s="3">
-        <v>-16100</v>
+        <v>-5700</v>
       </c>
       <c r="F32" s="3">
-        <v>-245400</v>
+        <v>-51900</v>
       </c>
       <c r="G32" s="3">
-        <v>-33100</v>
+        <v>2100</v>
       </c>
       <c r="H32" s="3">
-        <v>-55200</v>
+        <v>19100</v>
       </c>
       <c r="I32" s="3">
-        <v>-19000</v>
+        <v>-1000</v>
       </c>
       <c r="J32" s="3">
-        <v>-25600</v>
+        <v>4500</v>
       </c>
       <c r="K32" s="3">
         <v>-100</v>
@@ -2129,26 +2129,26 @@
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -2174,26 +2174,26 @@
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>153600</v>
-      </c>
-      <c r="E45" s="3">
-        <v>134400</v>
-      </c>
-      <c r="F45" s="3">
-        <v>92200</v>
-      </c>
-      <c r="G45" s="3">
-        <v>56100</v>
-      </c>
-      <c r="H45" s="3">
-        <v>39000</v>
-      </c>
-      <c r="I45" s="3">
-        <v>41900</v>
-      </c>
-      <c r="J45" s="3">
-        <v>44300</v>
+      <c r="D45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K45" s="3">
         <v>30000</v>
@@ -2264,17 +2264,17 @@
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3" t="s">
-        <v>3</v>
+      <c r="D47" s="3">
+        <v>195300</v>
       </c>
       <c r="E47" s="3">
         <v>252300</v>
       </c>
-      <c r="F47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G47" s="3" t="s">
-        <v>3</v>
+      <c r="F47" s="3">
+        <v>262700</v>
+      </c>
+      <c r="G47" s="3">
+        <v>169500</v>
       </c>
       <c r="H47" s="3">
         <v>55000</v>
@@ -2283,7 +2283,7 @@
         <v>43600</v>
       </c>
       <c r="J47" s="3">
-        <v>22700</v>
+        <v>43600</v>
       </c>
       <c r="K47" s="3">
         <v>11800</v>
@@ -2490,16 +2490,16 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>226600</v>
+        <v>31300</v>
       </c>
       <c r="E52" s="3">
-        <v>27300</v>
+        <v>27200</v>
       </c>
       <c r="F52" s="3">
-        <v>291300</v>
+        <v>28600</v>
       </c>
       <c r="G52" s="3">
-        <v>192600</v>
+        <v>23100</v>
       </c>
       <c r="H52" s="3">
         <v>10600</v>
@@ -2508,7 +2508,7 @@
         <v>23600</v>
       </c>
       <c r="J52" s="3">
-        <v>59000</v>
+        <v>38100</v>
       </c>
       <c r="K52" s="3">
         <v>35300</v>
@@ -2708,19 +2708,19 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>49300</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>46500</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>52400</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>41100</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>42200</v>
       </c>
       <c r="I58" s="3">
         <v>0</v>
@@ -2753,25 +2753,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>855200</v>
+        <v>710200</v>
       </c>
       <c r="E59" s="3">
-        <v>1033800</v>
+        <v>780900</v>
       </c>
       <c r="F59" s="3">
-        <v>726500</v>
+        <v>496400</v>
       </c>
       <c r="G59" s="3">
-        <v>595400</v>
+        <v>413300</v>
       </c>
       <c r="H59" s="3">
-        <v>452800</v>
+        <v>266600</v>
       </c>
       <c r="I59" s="3">
-        <v>261800</v>
+        <v>220200</v>
       </c>
       <c r="J59" s="3">
-        <v>275100</v>
+        <v>237400</v>
       </c>
       <c r="K59" s="3">
         <v>148300</v>
@@ -2843,25 +2843,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>3749400</v>
+        <v>4295700</v>
       </c>
       <c r="E61" s="3">
-        <v>3742500</v>
+        <v>4128800</v>
       </c>
       <c r="F61" s="3">
-        <v>2253100</v>
+        <v>2578600</v>
       </c>
       <c r="G61" s="3">
-        <v>1675200</v>
+        <v>1962500</v>
       </c>
       <c r="H61" s="3">
-        <v>891800</v>
+        <v>1195000</v>
       </c>
       <c r="I61" s="3">
-        <v>16800</v>
+        <v>0</v>
       </c>
       <c r="J61" s="3">
-        <v>16000</v>
+        <v>0</v>
       </c>
       <c r="K61" s="3">
         <v>15100</v>
@@ -2888,25 +2888,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>670100</v>
+        <v>123800</v>
       </c>
       <c r="E62" s="3">
-        <v>490700</v>
+        <v>104500</v>
       </c>
       <c r="F62" s="3">
-        <v>641300</v>
+        <v>315800</v>
       </c>
       <c r="G62" s="3">
-        <v>351800</v>
+        <v>64500</v>
       </c>
       <c r="H62" s="3">
-        <v>360600</v>
+        <v>57400</v>
       </c>
       <c r="I62" s="3">
-        <v>93600</v>
+        <v>110400</v>
       </c>
       <c r="J62" s="3">
-        <v>67000</v>
+        <v>83000</v>
       </c>
       <c r="K62" s="3">
         <v>32000</v>
@@ -3696,25 +3696,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>168400</v>
+        <v>87300</v>
       </c>
       <c r="E83" s="3">
-        <v>202200</v>
+        <v>69900</v>
       </c>
       <c r="F83" s="3">
-        <v>119100</v>
+        <v>55900</v>
       </c>
       <c r="G83" s="3">
-        <v>86700</v>
+        <v>53200</v>
       </c>
       <c r="H83" s="3">
-        <v>87200</v>
+        <v>53800</v>
       </c>
       <c r="I83" s="3">
-        <v>91600</v>
+        <v>49000</v>
       </c>
       <c r="J83" s="3">
-        <v>61300</v>
+        <v>29800</v>
       </c>
       <c r="K83" s="3">
         <v>29100</v>
@@ -4453,26 +4453,26 @@
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>

--- a/AAII_Financials/Yearly/SNAP_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/SNAP_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="92">
   <si>
     <t>SNAP</t>
   </si>
@@ -656,62 +656,62 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="6" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43830</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43465</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43100</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42735</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42369</v>
       </c>
-      <c r="M7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N7" s="2" t="s">
         <v>3</v>
       </c>
@@ -721,42 +721,45 @@
       <c r="P7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>5361400</v>
+      </c>
+      <c r="E8" s="3">
         <v>4606100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>4601800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>4117000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2506600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1715500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1180400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>824900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>404500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>58700</v>
       </c>
-      <c r="M8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N8" s="3" t="s">
         <v>3</v>
       </c>
@@ -766,42 +769,45 @@
       <c r="P8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>2473100</v>
+      </c>
+      <c r="E9" s="3">
         <v>2114100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1794800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1750200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1182500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>895800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>798900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>677600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>451700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>182300</v>
       </c>
-      <c r="M9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N9" s="3" t="s">
         <v>3</v>
       </c>
@@ -811,42 +817,45 @@
       <c r="P9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>2888300</v>
+      </c>
+      <c r="E10" s="3">
         <v>2492000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2807100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2366800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1324100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>819700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>381600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>147400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>-47200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>-123700</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N10" s="3" t="s">
         <v>3</v>
       </c>
@@ -856,9 +865,12 @@
       <c r="P10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q10" s="3"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -876,41 +888,42 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>1652800</v>
+      </c>
+      <c r="E12" s="3">
         <v>1910900</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>2030900</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>1565500</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>1101600</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>883500</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>772200</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>1534900</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>183700</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>82200</v>
       </c>
-      <c r="M12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N12" s="3" t="s">
         <v>3</v>
       </c>
@@ -920,9 +933,12 @@
       <c r="P12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q12" s="3"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -965,36 +981,39 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-      <c r="Q13" s="3"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>78800</v>
+      </c>
+      <c r="E14" s="3">
         <v>33700</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>225800</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-292000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-12900</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-39900</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>38300</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>39900</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1004,42 +1023,45 @@
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P14" s="3">
         <v>0</v>
       </c>
-      <c r="Q14" s="3"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>168400</v>
+        <v>154900</v>
       </c>
       <c r="E15" s="3">
+        <v>148500</v>
+      </c>
+      <c r="F15" s="3">
         <v>152900</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>119100</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>86700</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>87200</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>91600</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>61300</v>
       </c>
-      <c r="K15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1049,15 +1071,18 @@
       <c r="N15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O15" s="3">
-        <v>0</v>
+      <c r="O15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P15" s="3">
         <v>0</v>
       </c>
-      <c r="Q15" s="3"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1072,41 +1097,42 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>6078500</v>
+      </c>
+      <c r="E17" s="3">
         <v>6004500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>5808200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>4819100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>3368700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2818900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2417800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>4270700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>924900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>440400</v>
       </c>
-      <c r="M17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1116,42 +1142,45 @@
       <c r="P17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q17" s="3"/>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-717100</v>
+      </c>
+      <c r="E18" s="3">
         <v>-1398400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-1206400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-702100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-862100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-1103300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-1237300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-3445700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-520400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-381700</v>
       </c>
-      <c r="M18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1161,9 +1190,12 @@
       <c r="P18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q18" s="3"/>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1181,41 +1213,42 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>8200</v>
+      </c>
+      <c r="E20" s="3">
         <v>8700</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>5700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>51900</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-2100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-19100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>1000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-4500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>1200</v>
       </c>
-      <c r="M20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1225,42 +1258,45 @@
       <c r="P20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q20" s="3"/>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-1238600</v>
+        <v>-570500</v>
       </c>
       <c r="E21" s="3">
+        <v>-1258500</v>
+      </c>
+      <c r="F21" s="3">
         <v>-1059200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-634800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-773200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-997000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-1146700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-3379900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-491200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-365200</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1270,41 +1306,44 @@
       <c r="P21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q21" s="3"/>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>21600</v>
+      </c>
+      <c r="E22" s="3">
         <v>22000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>21500</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>17700</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>97200</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>25000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>3900</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>3500</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>1400</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
-      </c>
-      <c r="M22" s="3" t="s">
-        <v>3</v>
+      <c r="M22" s="3">
+        <v>0</v>
       </c>
       <c r="N22" s="3" t="s">
         <v>3</v>
@@ -1315,42 +1354,45 @@
       <c r="P22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q22" s="3"/>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-672200</v>
+      </c>
+      <c r="E23" s="3">
         <v>-1294400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-1400700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-474400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-926200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-1033300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-1253400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-3463400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-521700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-380500</v>
       </c>
-      <c r="M23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1360,42 +1402,45 @@
       <c r="P23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q23" s="3"/>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>25600</v>
+      </c>
+      <c r="E24" s="3">
         <v>28100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>29000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>13600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>18700</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>2500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-18300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-7100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-7600</v>
       </c>
-      <c r="M24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1405,9 +1450,12 @@
       <c r="P24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q24" s="3"/>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1450,42 +1498,45 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-      <c r="Q25" s="3"/>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-697900</v>
+      </c>
+      <c r="E26" s="3">
         <v>-1322500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-1429700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-488000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-944800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-1033700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-1255900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-3445100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-514600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-372900</v>
       </c>
-      <c r="M26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1495,42 +1546,45 @@
       <c r="P26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q26" s="3"/>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-697900</v>
+      </c>
+      <c r="E27" s="3">
         <v>-1322500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-1429700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-488000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-944800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-1033700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-1255900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-3445100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-514600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-372900</v>
       </c>
-      <c r="M27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1540,9 +1594,12 @@
       <c r="P27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q27" s="3"/>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1585,9 +1642,12 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-      <c r="Q28" s="3"/>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1627,12 +1687,15 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-      <c r="P29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q29" s="3"/>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R29" s="3"/>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1675,9 +1738,12 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-      <c r="Q30" s="3"/>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1720,42 +1786,45 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-      <c r="Q31" s="3"/>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3"/>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-8200</v>
+      </c>
+      <c r="E32" s="3">
         <v>-8700</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-5700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-51900</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>2100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>19100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-1000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>4500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-1200</v>
       </c>
-      <c r="M32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N32" s="3" t="s">
         <v>3</v>
       </c>
@@ -1765,42 +1834,45 @@
       <c r="P32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q32" s="3"/>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R32" s="3"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-697900</v>
+      </c>
+      <c r="E33" s="3">
         <v>-1322500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-1429700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-488000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-944800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-1033700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-1255900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-3445100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-514600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-372900</v>
       </c>
-      <c r="M33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1810,9 +1882,12 @@
       <c r="P33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q33" s="3"/>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R33" s="3"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1855,42 +1930,45 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-      <c r="Q34" s="3"/>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3"/>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-697900</v>
+      </c>
+      <c r="E35" s="3">
         <v>-1322500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-1429700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-488000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-944800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-1033700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-1255900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-3445100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-514600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-372900</v>
       </c>
-      <c r="M35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N35" s="3" t="s">
         <v>3</v>
       </c>
@@ -1900,47 +1978,50 @@
       <c r="P35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q35" s="3"/>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R35" s="3"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43830</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43465</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43100</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42735</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42369</v>
       </c>
-      <c r="M38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N38" s="2" t="s">
         <v>3</v>
       </c>
@@ -1950,9 +2031,12 @@
       <c r="P38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="Q38" s="2"/>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R38" s="2"/>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1970,8 +2054,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1989,41 +2074,42 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1046500</v>
+      </c>
+      <c r="E41" s="3">
         <v>1780400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1423100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1993800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>545600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>520300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>387100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>334100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>150100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>640800</v>
       </c>
-      <c r="M41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2033,41 +2119,44 @@
       <c r="P41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q41" s="3"/>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R41" s="3"/>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>2329700</v>
+      </c>
+      <c r="E42" s="3">
         <v>1763700</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>2516000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>1699100</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>1991900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>1592500</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>891900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>1709000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>837200</v>
       </c>
-      <c r="L42" s="3">
-        <v>0</v>
-      </c>
-      <c r="M42" s="3" t="s">
-        <v>3</v>
+      <c r="M42" s="3">
+        <v>0</v>
       </c>
       <c r="N42" s="3" t="s">
         <v>3</v>
@@ -2078,42 +2167,45 @@
       <c r="P42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q42" s="3"/>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R42" s="3"/>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1348500</v>
+      </c>
+      <c r="E43" s="3">
         <v>1278200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1183100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1068900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>744300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>492200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>355000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>279500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>162700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>44300</v>
       </c>
-      <c r="M43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2123,9 +2215,12 @@
       <c r="P43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q43" s="3"/>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R43" s="3"/>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2150,8 +2245,8 @@
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -2168,9 +2263,12 @@
       <c r="P44" s="3">
         <v>0</v>
       </c>
-      <c r="Q44" s="3"/>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3">
+        <v>0</v>
+      </c>
+      <c r="R44" s="3"/>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2195,15 +2293,15 @@
       <c r="J45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L45" s="3">
         <v>30000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>7400</v>
       </c>
-      <c r="M45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2213,42 +2311,45 @@
       <c r="P45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q45" s="3"/>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R45" s="3"/>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>4906800</v>
+      </c>
+      <c r="E46" s="3">
         <v>4975800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>5256600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>4854000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>3338000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2644000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1675900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2366800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1180000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>692600</v>
       </c>
-      <c r="M46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2258,42 +2359,45 @@
       <c r="P46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q46" s="3"/>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R46" s="3"/>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>188300</v>
+      </c>
+      <c r="E47" s="3">
         <v>195300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>252300</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>262700</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>169500</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>55000</v>
-      </c>
-      <c r="I47" s="3">
-        <v>43600</v>
       </c>
       <c r="J47" s="3">
         <v>43600</v>
       </c>
       <c r="K47" s="3">
+        <v>43600</v>
+      </c>
+      <c r="L47" s="3">
         <v>11800</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>9100</v>
       </c>
-      <c r="M47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2303,42 +2407,45 @@
       <c r="P47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q47" s="3"/>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R47" s="3"/>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1019500</v>
+      </c>
+      <c r="E48" s="3">
         <v>927200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>642700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>524900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>448400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>449100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>212600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>166800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>100600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>44100</v>
       </c>
-      <c r="M48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2348,42 +2455,45 @@
       <c r="P48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q48" s="3"/>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R48" s="3"/>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1776100</v>
+      </c>
+      <c r="E49" s="3">
         <v>1838100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1850600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1866100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1045200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>853300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>758400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>806400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>395100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>177200</v>
       </c>
-      <c r="M49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2393,9 +2503,12 @@
       <c r="P49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q49" s="3"/>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R49" s="3"/>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2438,9 +2551,12 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-      <c r="Q50" s="3"/>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3"/>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2483,42 +2599,45 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-      <c r="Q51" s="3"/>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3"/>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>45600</v>
+      </c>
+      <c r="E52" s="3">
         <v>31300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>27200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>28600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>23100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>10600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>23600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>38100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>35300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>16000</v>
       </c>
-      <c r="M52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2528,9 +2647,12 @@
       <c r="P52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q52" s="3"/>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R52" s="3"/>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2573,42 +2695,45 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-      <c r="Q53" s="3"/>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3"/>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>7936300</v>
+      </c>
+      <c r="E54" s="3">
         <v>7967800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>8029500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>7536300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>5024200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>4011900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2714100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>3421600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1722800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>938900</v>
       </c>
-      <c r="M54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2618,9 +2743,12 @@
       <c r="P54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q54" s="3"/>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R54" s="3"/>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2638,8 +2766,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2657,41 +2786,42 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>173200</v>
+      </c>
+      <c r="E57" s="3">
         <v>279000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>181800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>125300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>71900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>46900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>30900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>71200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>8400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>700</v>
       </c>
-      <c r="M57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2701,30 +2831,33 @@
       <c r="P57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q57" s="3"/>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R57" s="3"/>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>61100</v>
+      </c>
+      <c r="E58" s="3">
         <v>49300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>46500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>52400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>41100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>42200</v>
       </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
       <c r="J58" s="3">
         <v>0</v>
       </c>
@@ -2746,42 +2879,45 @@
       <c r="P58" s="3">
         <v>0</v>
       </c>
-      <c r="Q58" s="3"/>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+      <c r="R58" s="3"/>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>710200</v>
+        <v>791800</v>
       </c>
       <c r="E59" s="3">
+        <v>601100</v>
+      </c>
+      <c r="F59" s="3">
         <v>780900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>496400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>413300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>266600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>220200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>237400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>148300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>155600</v>
       </c>
-      <c r="M59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2791,42 +2927,45 @@
       <c r="P59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q59" s="3"/>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R59" s="3"/>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1243500</v>
+      </c>
+      <c r="E60" s="3">
         <v>1134100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1215600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>851800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>667300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>499700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>292700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>346300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>156700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>156300</v>
       </c>
-      <c r="M60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2836,42 +2975,45 @@
       <c r="P60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q60" s="3"/>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R60" s="3"/>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>4182800</v>
+      </c>
+      <c r="E61" s="3">
         <v>4295700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>4128800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2578600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1962500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1195000</v>
       </c>
-      <c r="I61" s="3">
-        <v>0</v>
-      </c>
       <c r="J61" s="3">
         <v>0</v>
       </c>
       <c r="K61" s="3">
+        <v>0</v>
+      </c>
+      <c r="L61" s="3">
         <v>15100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>13500</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
         <v>0</v>
       </c>
@@ -2881,42 +3023,45 @@
       <c r="P61" s="3">
         <v>0</v>
       </c>
-      <c r="Q61" s="3"/>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+      <c r="R61" s="3"/>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>59200</v>
+      </c>
+      <c r="E62" s="3">
         <v>123800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>104500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>315800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>64500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>57400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>110400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>83000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>32000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>5000</v>
       </c>
-      <c r="M62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2926,9 +3071,12 @@
       <c r="P62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q62" s="3"/>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R62" s="3"/>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2971,9 +3119,12 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-      <c r="Q63" s="3"/>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3"/>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3016,9 +3167,12 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-      <c r="Q64" s="3"/>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3"/>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3061,42 +3215,45 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-      <c r="Q65" s="3"/>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3"/>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>5485600</v>
+      </c>
+      <c r="E66" s="3">
         <v>5553600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>5448800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>3746100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2694300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1752000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>403100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>429200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>203900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>174800</v>
       </c>
-      <c r="M66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3106,9 +3263,12 @@
       <c r="P66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q66" s="3"/>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R66" s="3"/>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3126,8 +3286,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3170,9 +3331,12 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-      <c r="Q68" s="3"/>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3"/>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3215,9 +3379,12 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-      <c r="Q69" s="3"/>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3"/>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3260,9 +3427,12 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-      <c r="Q70" s="3"/>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3"/>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3305,42 +3475,45 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-      <c r="Q71" s="3"/>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3"/>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-12735500</v>
+      </c>
+      <c r="E72" s="3">
         <v>-11726500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-10214700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-8284500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-7891500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-6945900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-5912600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-4656700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-1207900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-693200</v>
       </c>
-      <c r="M72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3350,9 +3523,12 @@
       <c r="P72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q72" s="3"/>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R72" s="3"/>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3395,9 +3571,12 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-      <c r="Q73" s="3"/>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3"/>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3440,9 +3619,12 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-      <c r="Q74" s="3"/>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3"/>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3485,42 +3667,45 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-      <c r="Q75" s="3"/>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3"/>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2450800</v>
+      </c>
+      <c r="E76" s="3">
         <v>2414100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2580700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>3790200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2330000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2259900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2311000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2992300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1518900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>764100</v>
       </c>
-      <c r="M76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3530,9 +3715,12 @@
       <c r="P76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q76" s="3"/>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R76" s="3"/>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3575,47 +3763,50 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-      <c r="Q77" s="3"/>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3"/>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43830</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43465</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43100</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42735</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42369</v>
       </c>
-      <c r="M80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N80" s="2" t="s">
         <v>3</v>
       </c>
@@ -3625,42 +3816,45 @@
       <c r="P80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="Q80" s="2"/>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R80" s="2"/>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-697900</v>
+      </c>
+      <c r="E81" s="3">
         <v>-1322500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-1429700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-488000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-944800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-1033700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-1255900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-3445100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-514600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-372900</v>
       </c>
-      <c r="M81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N81" s="3" t="s">
         <v>3</v>
       </c>
@@ -3670,9 +3864,12 @@
       <c r="P81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q81" s="3"/>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R81" s="3"/>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3690,41 +3887,42 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>98100</v>
+      </c>
+      <c r="E83" s="3">
         <v>87300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>69900</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>55900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>53200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>53800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>49000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>29800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>29100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>15300</v>
       </c>
-      <c r="M83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N83" s="3" t="s">
         <v>3</v>
       </c>
@@ -3734,9 +3932,12 @@
       <c r="P83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q83" s="3"/>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R83" s="3"/>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3779,9 +3980,12 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-      <c r="Q84" s="3"/>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3"/>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3824,9 +4028,12 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-      <c r="Q85" s="3"/>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3"/>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3869,9 +4076,12 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-      <c r="Q86" s="3"/>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3"/>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3914,9 +4124,12 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-      <c r="Q87" s="3"/>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3"/>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3959,42 +4172,45 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-      <c r="Q88" s="3"/>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3"/>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>413500</v>
+      </c>
+      <c r="E89" s="3">
         <v>246500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>184600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>292900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-167600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-305000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-689900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-734700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-611200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-306600</v>
       </c>
-      <c r="M89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N89" s="3" t="s">
         <v>3</v>
       </c>
@@ -4004,9 +4220,12 @@
       <c r="P89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q89" s="3"/>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R89" s="3"/>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4024,41 +4243,42 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-194800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-211700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-129300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-69900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-57800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-36500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-120200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-84500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-66400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-19200</v>
       </c>
-      <c r="M91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N91" s="3" t="s">
         <v>3</v>
       </c>
@@ -4068,9 +4288,12 @@
       <c r="P91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q91" s="3"/>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R91" s="3"/>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4113,9 +4336,12 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-      <c r="Q92" s="3"/>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3"/>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4158,42 +4384,45 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-      <c r="Q93" s="3"/>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3"/>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-717100</v>
+      </c>
+      <c r="E94" s="3">
         <v>571000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1062300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>90200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-729900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-728600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>694500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1357000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1014300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-100900</v>
       </c>
-      <c r="M94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N94" s="3" t="s">
         <v>3</v>
       </c>
@@ -4203,9 +4432,12 @@
       <c r="P94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q94" s="3"/>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R94" s="3"/>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4223,8 +4455,9 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4267,9 +4500,12 @@
       <c r="P96" s="3">
         <v>0</v>
       </c>
-      <c r="Q96" s="3"/>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3"/>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4312,9 +4548,12 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-      <c r="Q97" s="3"/>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3"/>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4357,9 +4596,12 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-      <c r="Q98" s="3"/>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3"/>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4402,42 +4644,45 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-      <c r="Q99" s="3"/>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3"/>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-428600</v>
+      </c>
+      <c r="E100" s="3">
         <v>-458800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>306700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>1065100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>922800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>1165900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>47400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>2265300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>1141900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>650400</v>
       </c>
-      <c r="M100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N100" s="3" t="s">
         <v>3</v>
       </c>
@@ -4447,9 +4692,12 @@
       <c r="P100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q100" s="3"/>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R100" s="3"/>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4474,8 +4722,8 @@
       <c r="J101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -4492,42 +4740,45 @@
       <c r="P101" s="3">
         <v>0</v>
       </c>
-      <c r="Q101" s="3"/>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+      <c r="R101" s="3"/>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-732200</v>
+      </c>
+      <c r="E102" s="3">
         <v>358700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-570900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1448200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>25300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>132300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>52000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>173700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-483600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>242800</v>
       </c>
-      <c r="M102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N102" s="3" t="s">
         <v>3</v>
       </c>
@@ -4537,7 +4788,10 @@
       <c r="P102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q102" s="3"/>
+      <c r="Q102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/SNAP_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/SNAP_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="92">
   <si>
     <t>SNAP</t>
   </si>
@@ -656,65 +656,65 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="7" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="18" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44196</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43830</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43465</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43100</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42735</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42369</v>
       </c>
-      <c r="N7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O7" s="2" t="s">
         <v>3</v>
       </c>
@@ -724,45 +724,48 @@
       <c r="Q7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="R7" s="2"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="S7" s="2"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>5931400</v>
+      </c>
+      <c r="E8" s="3">
         <v>5361400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>4606100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>4601800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>4117000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>2506600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1715500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1180400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>824900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>404500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>58700</v>
       </c>
-      <c r="N8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O8" s="3" t="s">
         <v>3</v>
       </c>
@@ -772,45 +775,48 @@
       <c r="Q8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R8" s="3"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S8" s="3"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>2669600</v>
+      </c>
+      <c r="E9" s="3">
         <v>2473100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>2114100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1794800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1750200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1182500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>895800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>798900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>677600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>451700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>182300</v>
       </c>
-      <c r="N9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O9" s="3" t="s">
         <v>3</v>
       </c>
@@ -820,45 +826,48 @@
       <c r="Q9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R9" s="3"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S9" s="3"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>3261900</v>
+      </c>
+      <c r="E10" s="3">
         <v>2888300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2492000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2807100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>2366800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1324100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>819700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>381600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>147400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>-47200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>-123700</v>
       </c>
-      <c r="N10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O10" s="3" t="s">
         <v>3</v>
       </c>
@@ -868,9 +877,12 @@
       <c r="Q10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R10" s="3"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S10" s="3"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -889,44 +901,45 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>1793600</v>
+      </c>
+      <c r="E12" s="3">
         <v>1652800</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>1910900</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>2030900</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>1565500</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>1101600</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>883500</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>772200</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>1534900</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>183700</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>82200</v>
       </c>
-      <c r="N12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O12" s="3" t="s">
         <v>3</v>
       </c>
@@ -936,9 +949,12 @@
       <c r="Q12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R12" s="3"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S12" s="3"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -984,39 +1000,42 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-      <c r="R13" s="3"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>78800</v>
+        <v>-78500</v>
       </c>
       <c r="E14" s="3">
+        <v>72100</v>
+      </c>
+      <c r="F14" s="3">
         <v>33700</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>225800</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-292000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-12900</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-39900</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>38300</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>39900</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1026,45 +1045,48 @@
       <c r="O14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="P14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q14" s="3">
         <v>0</v>
       </c>
-      <c r="R14" s="3"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>163600</v>
+      </c>
+      <c r="E15" s="3">
         <v>154900</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>148500</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>152900</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>119100</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>86700</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>87200</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>91600</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>61300</v>
       </c>
-      <c r="L15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1074,15 +1096,18 @@
       <c r="O15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P15" s="3">
-        <v>0</v>
+      <c r="P15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q15" s="3">
         <v>0</v>
       </c>
-      <c r="R15" s="3"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+      <c r="S15" s="3"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1098,44 +1123,45 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>6463600</v>
+      </c>
+      <c r="E17" s="3">
         <v>6078500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>6004500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>5808200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>4819100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>3368700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2818900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2417800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>4270700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>924900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>440400</v>
       </c>
-      <c r="N17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1145,45 +1171,48 @@
       <c r="Q17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R17" s="3"/>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S17" s="3"/>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-532200</v>
+      </c>
+      <c r="E18" s="3">
         <v>-717100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-1398400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-1206400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-702100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-862100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-1103300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-1237300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-3445700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-520400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-381700</v>
       </c>
-      <c r="N18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1193,9 +1222,12 @@
       <c r="Q18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R18" s="3"/>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S18" s="3"/>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1214,44 +1246,45 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>8200</v>
+        <v>9600</v>
       </c>
       <c r="E20" s="3">
+        <v>14900</v>
+      </c>
+      <c r="F20" s="3">
         <v>8700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>5700</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>51900</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-2100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-19100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>1000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-4500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>1200</v>
       </c>
-      <c r="N20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1261,45 +1294,48 @@
       <c r="Q20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R20" s="3"/>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S20" s="3"/>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-570500</v>
+        <v>-378100</v>
       </c>
       <c r="E21" s="3">
+        <v>-577200</v>
+      </c>
+      <c r="F21" s="3">
         <v>-1258500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-1059200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-634800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-773200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-997000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-1146700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-3379900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-491200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-365200</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1309,44 +1345,47 @@
       <c r="Q21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R21" s="3"/>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S21" s="3"/>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>122000</v>
+      </c>
+      <c r="E22" s="3">
         <v>21600</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>22000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>21500</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>17700</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>97200</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>25000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>3900</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>3500</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>1400</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
-      </c>
-      <c r="N22" s="3" t="s">
-        <v>3</v>
+      <c r="N22" s="3">
+        <v>0</v>
       </c>
       <c r="O22" s="3" t="s">
         <v>3</v>
@@ -1357,45 +1396,48 @@
       <c r="Q22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R22" s="3"/>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S22" s="3"/>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-451100</v>
+      </c>
+      <c r="E23" s="3">
         <v>-672200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-1294400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-1400700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-474400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-926200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-1033300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-1253400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-3463400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-521700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-380500</v>
       </c>
-      <c r="N23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1405,45 +1447,48 @@
       <c r="Q23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R23" s="3"/>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S23" s="3"/>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>9400</v>
+      </c>
+      <c r="E24" s="3">
         <v>25600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>28100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>29000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>13600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>18700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>2500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-18300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-7100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-7600</v>
       </c>
-      <c r="N24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1453,9 +1498,12 @@
       <c r="Q24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R24" s="3"/>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S24" s="3"/>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1501,45 +1549,48 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-      <c r="R25" s="3"/>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3"/>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-460500</v>
+      </c>
+      <c r="E26" s="3">
         <v>-697900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-1322500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-1429700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-488000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-944800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-1033700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-1255900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-3445100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-514600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-372900</v>
       </c>
-      <c r="N26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1549,45 +1600,48 @@
       <c r="Q26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R26" s="3"/>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S26" s="3"/>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-460500</v>
+      </c>
+      <c r="E27" s="3">
         <v>-697900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-1322500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-1429700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-488000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-944800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-1033700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-1255900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-3445100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-514600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-372900</v>
       </c>
-      <c r="N27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1597,9 +1651,12 @@
       <c r="Q27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R27" s="3"/>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S27" s="3"/>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1645,9 +1702,12 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-      <c r="R28" s="3"/>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3"/>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1690,12 +1750,15 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-      <c r="Q29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R29" s="3"/>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S29" s="3"/>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1741,9 +1804,12 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-      <c r="R30" s="3"/>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3"/>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1789,45 +1855,48 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-      <c r="R31" s="3"/>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3"/>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-8200</v>
+        <v>-9600</v>
       </c>
       <c r="E32" s="3">
+        <v>-14900</v>
+      </c>
+      <c r="F32" s="3">
         <v>-8700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-5700</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-51900</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>2100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>19100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-1000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>4500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-1200</v>
       </c>
-      <c r="N32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O32" s="3" t="s">
         <v>3</v>
       </c>
@@ -1837,45 +1906,48 @@
       <c r="Q32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R32" s="3"/>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S32" s="3"/>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-460500</v>
+      </c>
+      <c r="E33" s="3">
         <v>-697900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-1322500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-1429700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-488000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-944800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-1033700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-1255900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-3445100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-514600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-372900</v>
       </c>
-      <c r="N33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1885,9 +1957,12 @@
       <c r="Q33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R33" s="3"/>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S33" s="3"/>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1933,45 +2008,48 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-      <c r="R34" s="3"/>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3"/>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-460500</v>
+      </c>
+      <c r="E35" s="3">
         <v>-697900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-1322500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-1429700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-488000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-944800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-1033700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-1255900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-3445100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-514600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-372900</v>
       </c>
-      <c r="N35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O35" s="3" t="s">
         <v>3</v>
       </c>
@@ -1981,50 +2059,53 @@
       <c r="Q35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R35" s="3"/>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S35" s="3"/>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44196</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43830</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43465</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43100</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42735</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42369</v>
       </c>
-      <c r="N38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2034,9 +2115,12 @@
       <c r="Q38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="R38" s="2"/>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="S38" s="2"/>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2055,8 +2139,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2075,44 +2160,45 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1030400</v>
+      </c>
+      <c r="E41" s="3">
         <v>1046500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1780400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1423100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1993800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>545600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>520300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>387100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>334100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>150100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>640800</v>
       </c>
-      <c r="N41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2122,44 +2208,47 @@
       <c r="Q41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R41" s="3"/>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S41" s="3"/>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>1910100</v>
+      </c>
+      <c r="E42" s="3">
         <v>2329700</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>1763700</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>2516000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>1699100</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>1991900</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>1592500</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>891900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>1709000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>837200</v>
       </c>
-      <c r="M42" s="3">
-        <v>0</v>
-      </c>
-      <c r="N42" s="3" t="s">
-        <v>3</v>
+      <c r="N42" s="3">
+        <v>0</v>
       </c>
       <c r="O42" s="3" t="s">
         <v>3</v>
@@ -2170,45 +2259,48 @@
       <c r="Q42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R42" s="3"/>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S42" s="3"/>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1372200</v>
+      </c>
+      <c r="E43" s="3">
         <v>1348500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1278200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1183100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1068900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>744300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>492200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>355000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>279500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>162700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>44300</v>
       </c>
-      <c r="N43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2218,9 +2310,12 @@
       <c r="Q43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R43" s="3"/>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S43" s="3"/>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2248,8 +2343,8 @@
       <c r="K44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -2266,9 +2361,12 @@
       <c r="Q44" s="3">
         <v>0</v>
       </c>
-      <c r="R44" s="3"/>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R44" s="3">
+        <v>0</v>
+      </c>
+      <c r="S44" s="3"/>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2296,15 +2394,15 @@
       <c r="K45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M45" s="3">
         <v>30000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>7400</v>
       </c>
-      <c r="N45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2314,45 +2412,48 @@
       <c r="Q45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R45" s="3"/>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S45" s="3"/>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>4584900</v>
+      </c>
+      <c r="E46" s="3">
         <v>4906800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>4975800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>5256600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>4854000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>3338000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2644000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1675900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2366800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1180000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>692600</v>
       </c>
-      <c r="N46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2362,45 +2463,48 @@
       <c r="Q46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R46" s="3"/>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S46" s="3"/>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>183700</v>
+      </c>
+      <c r="E47" s="3">
         <v>188300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>195300</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>252300</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>262700</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>169500</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>55000</v>
-      </c>
-      <c r="J47" s="3">
-        <v>43600</v>
       </c>
       <c r="K47" s="3">
         <v>43600</v>
       </c>
       <c r="L47" s="3">
+        <v>43600</v>
+      </c>
+      <c r="M47" s="3">
         <v>11800</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>9100</v>
       </c>
-      <c r="N47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2410,45 +2514,48 @@
       <c r="Q47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R47" s="3"/>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S47" s="3"/>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1084300</v>
+      </c>
+      <c r="E48" s="3">
         <v>1019500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>927200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>642700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>524900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>448400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>449100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>212600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>166800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>100600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>44100</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2458,45 +2565,48 @@
       <c r="Q48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R48" s="3"/>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S48" s="3"/>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1787400</v>
+      </c>
+      <c r="E49" s="3">
         <v>1776100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1838100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1850600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1866100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1045200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>853300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>758400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>806400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>395100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>177200</v>
       </c>
-      <c r="N49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2506,9 +2616,12 @@
       <c r="Q49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R49" s="3"/>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S49" s="3"/>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2554,9 +2667,12 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-      <c r="R50" s="3"/>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3"/>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2602,45 +2718,48 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-      <c r="R51" s="3"/>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3"/>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>37500</v>
+      </c>
+      <c r="E52" s="3">
         <v>45600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>31300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>27200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>28600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>23100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>10600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>23600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>38100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>35300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>16000</v>
       </c>
-      <c r="N52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2650,9 +2769,12 @@
       <c r="Q52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R52" s="3"/>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S52" s="3"/>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2698,45 +2820,48 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-      <c r="R53" s="3"/>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3"/>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>7677800</v>
+      </c>
+      <c r="E54" s="3">
         <v>7936300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>7967800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>8029500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>7536300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>5024200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>4011900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2714100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>3421600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1722800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>938900</v>
       </c>
-      <c r="N54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2746,9 +2871,12 @@
       <c r="Q54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R54" s="3"/>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S54" s="3"/>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2767,8 +2895,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2787,44 +2916,45 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>219800</v>
+      </c>
+      <c r="E57" s="3">
         <v>173200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>279000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>181800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>125300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>71900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>46900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>30900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>71200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>8400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>700</v>
       </c>
-      <c r="N57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2834,33 +2964,36 @@
       <c r="Q57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R57" s="3"/>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S57" s="3"/>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>95400</v>
+      </c>
+      <c r="E58" s="3">
         <v>61100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>49300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>46500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>52400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>41100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>42200</v>
       </c>
-      <c r="J58" s="3">
-        <v>0</v>
-      </c>
       <c r="K58" s="3">
         <v>0</v>
       </c>
@@ -2882,45 +3015,48 @@
       <c r="Q58" s="3">
         <v>0</v>
       </c>
-      <c r="R58" s="3"/>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R58" s="3">
+        <v>0</v>
+      </c>
+      <c r="S58" s="3"/>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>761100</v>
+      </c>
+      <c r="E59" s="3">
         <v>791800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>601100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>780900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>496400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>413300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>266600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>220200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>237400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>148300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>155600</v>
       </c>
-      <c r="N59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2930,45 +3066,48 @@
       <c r="Q59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R59" s="3"/>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S59" s="3"/>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1286900</v>
+      </c>
+      <c r="E60" s="3">
         <v>1243500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1134100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1215600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>851800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>667300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>499700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>292700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>346300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>156700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>156300</v>
       </c>
-      <c r="N60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2978,45 +3117,48 @@
       <c r="Q60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R60" s="3"/>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S60" s="3"/>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>4047700</v>
+      </c>
+      <c r="E61" s="3">
         <v>4182800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>4295700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>4128800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2578600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1962500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1195000</v>
       </c>
-      <c r="J61" s="3">
-        <v>0</v>
-      </c>
       <c r="K61" s="3">
         <v>0</v>
       </c>
       <c r="L61" s="3">
+        <v>0</v>
+      </c>
+      <c r="M61" s="3">
         <v>15100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>13500</v>
       </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
       <c r="O61" s="3">
         <v>0</v>
       </c>
@@ -3026,45 +3168,48 @@
       <c r="Q61" s="3">
         <v>0</v>
       </c>
-      <c r="R61" s="3"/>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R61" s="3">
+        <v>0</v>
+      </c>
+      <c r="S61" s="3"/>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>61800</v>
+      </c>
+      <c r="E62" s="3">
         <v>59200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>123800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>104500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>315800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>64500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>57400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>110400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>83000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>32000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>5000</v>
       </c>
-      <c r="N62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3074,9 +3219,12 @@
       <c r="Q62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R62" s="3"/>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S62" s="3"/>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3122,9 +3270,12 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-      <c r="R63" s="3"/>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3"/>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3170,9 +3321,12 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-      <c r="R64" s="3"/>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3"/>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3218,45 +3372,48 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-      <c r="R65" s="3"/>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3"/>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>5396300</v>
+      </c>
+      <c r="E66" s="3">
         <v>5485600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>5553600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>5448800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>3746100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2694300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1752000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>403100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>429200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>203900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>174800</v>
       </c>
-      <c r="N66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3266,9 +3423,12 @@
       <c r="Q66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R66" s="3"/>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S66" s="3"/>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3287,8 +3447,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3334,9 +3495,12 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-      <c r="R68" s="3"/>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3"/>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3382,9 +3546,12 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-      <c r="R69" s="3"/>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3"/>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3430,9 +3597,12 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-      <c r="R70" s="3"/>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3"/>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3478,45 +3648,48 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-      <c r="R71" s="3"/>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3"/>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-13946800</v>
+      </c>
+      <c r="E72" s="3">
         <v>-12735500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-11726500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-10214700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-8284500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-7891500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-6945900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-5912600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-4656700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-1207900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-693200</v>
       </c>
-      <c r="N72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3526,9 +3699,12 @@
       <c r="Q72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R72" s="3"/>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S72" s="3"/>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3574,9 +3750,12 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-      <c r="R73" s="3"/>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3"/>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3622,9 +3801,12 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-      <c r="R74" s="3"/>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3"/>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3670,45 +3852,48 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-      <c r="R75" s="3"/>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3"/>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2281500</v>
+      </c>
+      <c r="E76" s="3">
         <v>2450800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2414100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2580700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>3790200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2330000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2259900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2311000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2992300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1518900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>764100</v>
       </c>
-      <c r="N76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3718,9 +3903,12 @@
       <c r="Q76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R76" s="3"/>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S76" s="3"/>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3766,50 +3954,53 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-      <c r="R77" s="3"/>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3"/>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44196</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43830</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43465</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43100</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42735</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42369</v>
       </c>
-      <c r="N80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O80" s="2" t="s">
         <v>3</v>
       </c>
@@ -3819,45 +4010,48 @@
       <c r="Q80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="R80" s="2"/>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="S80" s="2"/>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-460500</v>
+      </c>
+      <c r="E81" s="3">
         <v>-697900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-1322500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-1429700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-488000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-944800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-1033700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-1255900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-3445100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-514600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-372900</v>
       </c>
-      <c r="N81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O81" s="3" t="s">
         <v>3</v>
       </c>
@@ -3867,9 +4061,12 @@
       <c r="Q81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R81" s="3"/>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S81" s="3"/>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3888,44 +4085,45 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>118100</v>
+      </c>
+      <c r="E83" s="3">
         <v>98100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>87300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>69900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>55900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>53200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>53800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>49000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>29800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>29100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>15300</v>
       </c>
-      <c r="N83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O83" s="3" t="s">
         <v>3</v>
       </c>
@@ -3935,9 +4133,12 @@
       <c r="Q83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R83" s="3"/>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S83" s="3"/>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3983,9 +4184,12 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-      <c r="R84" s="3"/>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3"/>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4031,9 +4235,12 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-      <c r="R85" s="3"/>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3"/>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4079,9 +4286,12 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-      <c r="R86" s="3"/>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3"/>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4127,9 +4337,12 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-      <c r="R87" s="3"/>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3"/>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4175,45 +4388,48 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-      <c r="R88" s="3"/>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3"/>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>656200</v>
+      </c>
+      <c r="E89" s="3">
         <v>413500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>246500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>184600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>292900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-167600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-305000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-689900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-734700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-611200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-306600</v>
       </c>
-      <c r="N89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O89" s="3" t="s">
         <v>3</v>
       </c>
@@ -4223,9 +4439,12 @@
       <c r="Q89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R89" s="3"/>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S89" s="3"/>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4244,44 +4463,45 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-219000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-194800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-211700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-129300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-69900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-57800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-36500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-120200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-84500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-66400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-19200</v>
       </c>
-      <c r="N91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O91" s="3" t="s">
         <v>3</v>
       </c>
@@ -4291,9 +4511,12 @@
       <c r="Q91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R91" s="3"/>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S91" s="3"/>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4339,9 +4562,12 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-      <c r="R92" s="3"/>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3"/>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4387,45 +4613,48 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-      <c r="R93" s="3"/>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3"/>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>173100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-717100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>571000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1062300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>90200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-729900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-728600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>694500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1357000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1014300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-100900</v>
       </c>
-      <c r="N94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O94" s="3" t="s">
         <v>3</v>
       </c>
@@ -4435,9 +4664,12 @@
       <c r="Q94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R94" s="3"/>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S94" s="3"/>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4456,8 +4688,9 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4503,9 +4736,12 @@
       <c r="Q96" s="3">
         <v>0</v>
       </c>
-      <c r="R96" s="3"/>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3"/>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4551,9 +4787,12 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-      <c r="R97" s="3"/>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3"/>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4599,9 +4838,12 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-      <c r="R98" s="3"/>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3"/>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4647,45 +4889,48 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-      <c r="R99" s="3"/>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3"/>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-848100</v>
+      </c>
+      <c r="E100" s="3">
         <v>-428600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-458800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>306700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>1065100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>922800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>1165900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>47400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>2265300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>1141900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>650400</v>
       </c>
-      <c r="N100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O100" s="3" t="s">
         <v>3</v>
       </c>
@@ -4695,9 +4940,12 @@
       <c r="Q100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R100" s="3"/>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S100" s="3"/>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4725,8 +4973,8 @@
       <c r="K101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -4743,45 +4991,48 @@
       <c r="Q101" s="3">
         <v>0</v>
       </c>
-      <c r="R101" s="3"/>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R101" s="3">
+        <v>0</v>
+      </c>
+      <c r="S101" s="3"/>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-18800</v>
+      </c>
+      <c r="E102" s="3">
         <v>-732200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>358700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-570900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>1448200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>25300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>132300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>52000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>173700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-483600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>242800</v>
       </c>
-      <c r="N102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O102" s="3" t="s">
         <v>3</v>
       </c>
@@ -4791,7 +5042,10 @@
       <c r="Q102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R102" s="3"/>
+      <c r="R102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
